--- a/outputs/evaluation/architecture/validation/CF_M09/run_2/CF_M09_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/validation/CF_M09/run_2/CF_M09_arch_eval.xlsx
@@ -451,10 +451,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7391</v>
+        <v>0.8276</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3617</v>
+        <v>0.5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -469,13 +469,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8421</v>
+        <v>0.88</v>
       </c>
       <c r="C3" t="n">
-        <v>0.381</v>
+        <v>0.5116000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9448</v>
+        <v>0.9635</v>
       </c>
     </row>
     <row r="4">
@@ -485,13 +485,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7516</v>
+        <v>0.8169</v>
       </c>
     </row>
     <row r="7">
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7059</v>
+        <v>0.8333</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -533,10 +533,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6875</v>
+        <v>0.6364</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8245</v>
+        <v>0.8092</v>
       </c>
     </row>
     <row r="10">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7647</v>
+        <v>0.75</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2</v>
+        <v>0.125</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -639,19 +639,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C2" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7857</v>
+        <v>0.8889</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3235</v>
+        <v>0.4571</v>
       </c>
     </row>
     <row r="3">
@@ -664,16 +664,16 @@
         <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0.8571</v>
       </c>
       <c r="F3" t="n">
-        <v>0.625</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="4">
@@ -689,13 +689,13 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
     </row>
   </sheetData>
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3">
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5">
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8">
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7391</v>
+        <v>0.8276</v>
       </c>
     </row>
     <row r="9">
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3617</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="10">
@@ -877,25 +877,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C2" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D2" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E2" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F2" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G2" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H2" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3">
@@ -911,19 +911,19 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4">
@@ -933,25 +933,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C4" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D4" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E4" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F4" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="G4" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H4" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5">
@@ -961,25 +961,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C5" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E5" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F5" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G5" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H5" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6">
@@ -989,25 +989,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C6" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D6" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E6" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F6" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="G6" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H6" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7">
@@ -1020,22 +1020,22 @@
         <v>41</v>
       </c>
       <c r="C7" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E7" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F7" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G7" t="n">
         <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8">
@@ -1063,7 +1063,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -1077,7 +1077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T18"/>
+  <dimension ref="A1:T25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1185,7 +1185,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AU_16</t>
+          <t>AU_19</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.7516</v>
+        <v>0.7913</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Estas peticiones son procesadas y enviadas mediante una conexi´ on interna al servicio functional, que es el que contiene la informaci´ on sensible del sistema. La comunicaci´ on se realiza mediante el protocolo de comunicaci´ on TCP.</t>
+          <t>These requests are processed and sent through an internal connection to the functional service, which is the one that contains the sensitive information of the system. The communication is performed using the TCP communication protocol.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1225,7 +1225,7 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>AU_16</t>
+          <t>AU_19</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Service responsible for user management, authentication, and authorization, and processing requests to the functional service.</t>
+          <t>Service responsible for user management, authentication and authorization, defining REST API routes and processing requests.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1349,81 +1349,77 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AU_10</t>
+          <t>P_04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CF_M09_AU23</t>
+          <t>CF_M09_P04</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>pattern</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.8023</v>
+        <v>0.8309</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS RDS</t>
+          <t>Observer</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Relational database service used to store system information.</t>
+          <t>The observer pattern defines a one-to-many dependency between objects, so that when one object changes its state, all objects that depend on it are notified and updated automatically.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>['AU_05']</t>
-        </is>
-      </c>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>AU_10</t>
+          <t>P_04</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>RDS</t>
+          <t>Observer pattern</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>RDS is a distributed relational database service. In the case of Waapiti, a MySQL database is used and contains all the system information.</t>
+          <t>The observer pattern is a software design pattern that defines a one-to-many dependency between objects, so that when one object changes its state, all objects that depend on it are notified and updated automatically.</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>CF_M09_AU39</t>
+          <t>CF_M09_P03</t>
         </is>
       </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
-          <t>CF_M09_AU23</t>
+          <t>CF_M09_P04</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
@@ -1431,80 +1427,84 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P_04</t>
+          <t>AU_18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CF_M09_P04</t>
+          <t>CF_M09_AU07</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.8309</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Observer</t>
-        </is>
-      </c>
+        <v>0.8425</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>The observer pattern defines a one-to-many dependency between objects, so that when one object changes its state, all objects that depend on it are notified and updated automatically.</t>
+          <t>The client is the user of the platform. [...] The server is the software that is responsible for processing user requests. [...] The communication between both is performed through the internet using the REST API model and the HTTP communication protocol.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>['AU_01', 'AU_02']</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>P_04</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Observer pattern</t>
-        </is>
-      </c>
+          <t>AU_18</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>client, server</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>The observer pattern is a software design pattern that defines a one-to-many dependency between objects, so that when one object changes its state, all objects that depend on it are notified and updated automatically.</t>
+          <t>On one side is the client, who makes the various requests, and on the other side is the server, who receives and processes them.</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>CF_M09_P03</t>
+          <t>CF_M09_AU06, CF_M09_AU05</t>
         </is>
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
-          <t>CF_M09_P04</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr"/>
+          <t>CF_M09_AU07</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>client, waapiti platform</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1587,12 +1587,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P_01</t>
+          <t>P_07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CF_M09_P01</t>
+          <t>CF_M09_P07</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1601,59 +1601,63 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.9061</v>
+        <v>0.8833</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Client-Server</t>
+          <t>Hook</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>The platform is a web service that follows the client-server architecture.</t>
+          <t>Hooks are functions that allow hooking into React state and other features.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>59</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>P_01</t>
+          <t>P_07</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Client-Server Architecture</t>
+          <t>Hook pattern</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>The Waapiti platform is a web service, therefore, as is usual in this type of software, it follows the client-server architecture.</t>
+          <t>Hooks are a new feature in React that allows you to use state and other React features without writing a class.</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>55</v>
-      </c>
-      <c r="Q7" t="inlineStr"/>
+        <v>59</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>CF_M09_AU01</t>
+        </is>
+      </c>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
-          <t>CF_M09_P01</t>
+          <t>CF_M09_P07</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
@@ -1661,35 +1665,35 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AU_04</t>
+          <t>P_01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CF_M09_AU19</t>
+          <t>CF_M09_P01</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>pattern</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.9173</v>
+        <v>0.9061</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Business Layer</t>
+          <t>Client-Server</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>It is the layer that is responsible for processing information, which is the server.</t>
+          <t>The platform is a web service that follows the client-server architecture, where the client makes requests to a server that processes them and returns the response.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1701,37 +1705,33 @@
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>AU_04</t>
+          <t>P_01</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Business layer (Backend)</t>
+          <t>Client-Server Architecture</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t xml:space="preserve">The business layer is divided into two services hosted on different machines. </t>
+          <t>The Waapiti platform is a web service, therefore, as is usual in this type of software, it follows the client-server architecture.</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>57</v>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>CF_M09_P02</t>
-        </is>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
-          <t>CF_M09_AU19</t>
+          <t>CF_M09_P01</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
@@ -1739,12 +1739,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AU_03</t>
+          <t>AU_04</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CF_M09_AU08</t>
+          <t>CF_M09_AU19</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1753,11 +1753,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.989</v>
+        <v>0.9173</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Presentation Layer</t>
+          <t>Business Layer</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>It is the layer that is responsible for displaying information to the user, which is the web browser.</t>
+          <t>This layer is the core of the application and is responsible for processing all the information.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1779,13 +1779,13 @@
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>AU_03</t>
+          <t>AU_04</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Presentation layer</t>
+          <t>Business layer (Backend)</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1795,11 +1795,11 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>This layer is responsible for displaying information to the user.</t>
+          <t xml:space="preserve">The business layer is divided into two services hosted on different machines. </t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
-          <t>CF_M09_AU08</t>
+          <t>CF_M09_AU19</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
@@ -1817,12 +1817,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AU_05</t>
+          <t>AU_03</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CF_M09_AU10</t>
+          <t>CF_M09_AU08</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1831,11 +1831,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.9923</v>
+        <v>0.989</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Layer</t>
+          <t>Presentation Layer</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>It is the layer that is responsible for storing all the data.</t>
+          <t>It is the layer that is responsible for displaying information to the user.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1857,13 +1857,13 @@
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>AU_05</t>
+          <t>AU_03</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Data layer</t>
+          <t>Presentation layer</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1873,7 +1873,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>This is the layer responsible for storing information.</t>
+          <t>This layer is responsible for displaying information to the user.</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -1887,7 +1887,7 @@
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
-          <t>CF_M09_AU10</t>
+          <t>CF_M09_AU08</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
@@ -1895,12 +1895,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AU_08</t>
+          <t>AU_05</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CF_M09_AU01</t>
+          <t>CF_M09_AU10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1909,67 +1909,63 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>0.9923</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>React</t>
+          <t>Data Layer</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>JavaScript library used for building user interfaces in the frontend.</t>
+          <t>It is the layer that is responsible for storing all the data.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>56, 60</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>['AU_03']</t>
-        </is>
-      </c>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>AU_08</t>
+          <t>AU_05</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>React</t>
+          <t>Data layer</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Within the software engineering specialization, this project focuses on web technologies, specifically using React [2] and Nest [3] for the codebase and AWS cloud services [4] for the infrastructure.</t>
+          <t>This is the layer responsible for storing information.</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>CF_M09_AU34</t>
+          <t>CF_M09_P02</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
-          <t>CF_M09_AU01</t>
+          <t>CF_M09_AU10</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
@@ -1977,12 +1973,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AU_09</t>
+          <t>AU_08</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CF_M09_AU02</t>
+          <t>CF_M09_AU01</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1995,7 +1991,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>NestJS</t>
+          <t>React</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2005,29 +2001,29 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Framework for building backend applications.</t>
+          <t>JavaScript library used for building user interfaces and frontend components.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>60, 69</t>
+          <t>56, 60</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>['AU_06', 'AU_07']</t>
+          <t>['AU_03']</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>AU_09</t>
+          <t>AU_08</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>NestJS</t>
+          <t>React</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2045,13 +2041,13 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>CF_M09_AU33</t>
+          <t>CF_M09_AU34</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
-          <t>CF_M09_AU02</t>
+          <t>CF_M09_AU01</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
@@ -2059,12 +2055,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AU_01</t>
+          <t>AU_11</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CF_M09_AU06</t>
+          <t>CF_M09_AU24</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2077,59 +2073,63 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Client</t>
+          <t>MySQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>The client is the user of the platform, who makes requests to the server.</t>
+          <t>Relational database management system used within AWS RDS.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>58, 76</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>['AU_05']</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>AU_01</t>
+          <t>AU_11</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Client</t>
+          <t>MySQL</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>On one side is the client, who makes the various requests, and on the other side is the server, who receives and processes them.</t>
+          <t>RDS is a distributed relational database service. In the case of Waapiti, a MySQL database is used and contains all the system information.</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>CF_M09_P01</t>
+          <t>CF_M09_AU23</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
-          <t>CF_M09_AU06</t>
+          <t>CF_M09_AU24</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
@@ -2137,12 +2137,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AU_11</t>
+          <t>AU_22</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CF_M09_AU25</t>
+          <t>CF_M09_AU22</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Amazon S3</t>
+          <t>REST</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2165,39 +2165,39 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Object storage service used to store multimedia files.</t>
+          <t>The communication between both is performed through the internet using the REST API model and the HTTP communication protocol.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>55</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>['AU_05']</t>
+          <t>['AU_18']</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>AU_11</t>
+          <t>AU_22</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Amazon S3</t>
+          <t>REST</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>This is AWS's object storage service.</t>
+          <t>Defines REST API routes and processes requests to send them to the functional service.</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -2205,13 +2205,13 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>CF_M09_AU39</t>
+          <t>CF_M09_AU20</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
-          <t>CF_M09_AU25</t>
+          <t>CF_M09_AU22</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
@@ -2219,17 +2219,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P_03</t>
+          <t>AU_14</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CF_M09_P03</t>
+          <t>CF_M09_AU40</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -2237,63 +2237,59 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Flux</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Flux is an architecture for frontend development based on the MVC design pattern with unidirectional communication.</t>
+          <t>Communication protocol used between client and server.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>55</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>['AU_03']</t>
+          <t>['AU_18']</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>P_03</t>
+          <t>AU_14</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Flux</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>A logical architecture called Flux has been used for the development of the presentation layer.</t>
+          <t xml:space="preserve">Communication between the two is carried out via the internet using the REST API model [30] and the HTTP communication protocol </t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>56</v>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>CF_M09_AU34</t>
-        </is>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
-          <t>CF_M09_P03</t>
+          <t>CF_M09_AU40</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
@@ -2301,17 +2297,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P_02</t>
+          <t>AU_09</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CF_M09_P02</t>
+          <t>CF_M09_AU02</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -2319,59 +2315,63 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Three Layers</t>
+          <t>NestJS</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>This architecture divides the system into three parts: presentation layer, business layer, and data layer.</t>
+          <t>NodeJS framework used to create backend applications and REST APIs.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>60, 68</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>['P_01']</t>
+          <t>['AU_06', 'AU_07']</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>P_02</t>
+          <t>AU_09</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Three Layers</t>
+          <t>NestJS</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>To decouple the components of the client-server model, a three-tier architecture has been used.</t>
+          <t>Within the software engineering specialization, this project focuses on web technologies, specifically using React [2] and Nest [3] for the codebase and AWS cloud services [4] for the infrastructure.</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>55</v>
-      </c>
-      <c r="Q16" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>CF_M09_AU33</t>
+        </is>
+      </c>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
-          <t>CF_M09_P02</t>
+          <t>CF_M09_AU02</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
@@ -2379,12 +2379,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AU_12</t>
+          <t>AU_17</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CF_M09_AU27</t>
+          <t>CF_M09_AU29</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Amazon DynamoDB</t>
+          <t>TypeORM</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cache system for users to improve response speed.</t>
+          <t>ORM used for database entity mapping and queries.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>60, 68</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2423,37 +2423,37 @@
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>AU_12</t>
+          <t>AU_17</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Amazon DynamoDB</t>
+          <t>TypeORM</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>To improve system response speed, there is a user cache system stored in Amazon DynamoDB</t>
+          <t>is an ORM (Object Relational Mapping) [41] for TypeScript and JavaScript.</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>CF_M09_AU10</t>
+          <t>CF_M09_AU33</t>
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
-          <t>CF_M09_AU27</t>
+          <t>CF_M09_AU29</t>
         </is>
       </c>
       <c r="T17" t="inlineStr"/>
@@ -2461,12 +2461,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AU_14</t>
+          <t>AU_01</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CF_M09_AU21</t>
+          <t>CF_M09_AU06</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2479,66 +2479,628 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>TCP</t>
+          <t>Client</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Communication protocol used between business and functional services.</t>
+          <t>The client is the user of the platform.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>['AU_16']</t>
-        </is>
-      </c>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>AU_14</t>
+          <t>AU_01</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>TCP</t>
+          <t>Client</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Communication is carried out using the TCP communication protocol</t>
+          <t>On one side is the client, who makes the various requests, and on the other side is the server, who receives and processes them.</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>CF_M09_AU20</t>
+          <t>CF_M09_P01</t>
         </is>
       </c>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
+          <t>CF_M09_AU06</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>AU_12</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>CF_M09_AU25</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Amazon S3</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>AWS object storage service used to store multimedia files.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>['AU_05']</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>AU_12</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Amazon S3</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>This is AWS's object storage service.</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>CF_M09_AU39</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>CF_M09_AU25</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>AU_16</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>CF_M09_AU17</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Redux</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>JavaScript library used to implement the Flux architecture.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>['AU_03']</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>AU_16</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Redux</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Redux is a JavaScript library that allows you to implement the Flux architecture.</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>56</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>CF_M09_P03</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>CF_M09_AU17</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>P_03</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>CF_M09_P03</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>pattern</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Flux</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Architectural Pattern</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Flux is a frontend architecture based on the MVC design pattern, but with unidirectional communication.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>['AU_03']</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>P_03</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Flux</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Architectural Pattern</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>A logical architecture called Flux has been used for the development of the presentation layer.</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>56</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>CF_M09_AU34</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>CF_M09_P03</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>AU_10</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>CF_M09_AU03</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AWS</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Cloud computing services used for infrastructure, including RDS, S3, and DynamoDB.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>58, 61</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>['AU_05']</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>AU_10</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>AWS</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Within the software engineering specialization, this project focuses on web technologies, specifically using React [2] and Nest [3] for the codebase and AWS cloud services [4] for the infrastructure.</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>CF_M09_AU03</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>P_02</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>CF_M09_P02</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>pattern</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Three Layers</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Architectural Pattern</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>This architecture divides the system into three parts, the presentation layer, the business layer and the data layer.</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>['P_01']</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>P_02</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Three Layers</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Architectural Pattern</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>To decouple the components of the client-server model, a three-tier architecture has been used.</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>CF_M09_P02</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>AU_13</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>CF_M09_AU27</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Amazon DynamoDB</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>AWS NoSQL database service used for user caching.</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>['AU_05']</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>AU_13</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Amazon DynamoDB</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>To improve system response speed, there is a user cache system stored in Amazon DynamoDB</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>CF_M09_AU10</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>CF_M09_AU27</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>AU_15</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
           <t>CF_M09_AU21</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>TCP</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Communication protocol used for internal communication between business and functional services.</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>['AU_19']</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>AU_15</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>TCP</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Communication is carried out using the TCP communication protocol</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>CF_M09_AU20</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>CF_M09_AU21</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2551,7 +3113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2615,7 +3177,7 @@
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>The server is the software that is responsible for receiving and processing user requests.</t>
+          <t>The server is the software that is responsible for processing user requests.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -2671,39 +3233,43 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AU_13</t>
+          <t>AU_20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>HTTP</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>functional service, data layer</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Communication protocol used between client and server.</t>
+          <t>This is the service that performs all the important logic of the platform. It is the service that has communication with the data layer.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CF_M09_AU38</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>CF_M09_AU19</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Business layer (Backend)</t>
+        </is>
+      </c>
       <c r="H4" t="n">
-        <v>0.7066</v>
+        <v>0.772</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AU_15</t>
+          <t>AU_21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2714,94 +3280,62 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>presentation layer, business layer</t>
+          <t>business service, amazon dynamodb</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>La comunicaci´ on entre ambos se realiza a trav´ es de internet utilizando el modelo de REST API [...] y el protocolo de comunicaci´ on HTTP.</t>
+          <t>For better response speed of the system, there is a user cache system stored in Amazon DynamoDB, to which the business service has access.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CF_M09_AU07</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>CF_M09_AU27</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Amazon DynamoDB</t>
+        </is>
+      </c>
       <c r="H5" t="n">
-        <v>0.7159</v>
+        <v>0.7688</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AU_17</t>
+          <t>P_06</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>functional service, data layer</t>
-        </is>
-      </c>
+          <t>Design Pattern</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Es el servicio que tiene comunicaci´ on con la capa de datos.</t>
+          <t>This pattern allows encapsulating information and exposing only what is desired to be shared between modules.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CF_M09_AU10</t>
+          <t>CF_M09_AU35</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Data layer</t>
+          <t>Modules</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.7706</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>AU_18</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>business service, amazon dynamodb</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Existe un sistema de cach´ e de usuarios almacenada en Amazon DynamoDB, a la cu´ al tiene acceso el servicio business.</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>CF_M09_AU27</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Amazon DynamoDB</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>0.7868000000000001</v>
+        <v>0.9649</v>
       </c>
     </row>
   </sheetData>
@@ -2815,7 +3349,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2863,151 +3397,151 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CF_M09_AU03</t>
+          <t>CF_M09_AU04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Device</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AWS</t>
+          <t>Player</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Within the software engineering specialization, this project focuses on web technologies, specifically using React [2] and Nest [3] for the codebase and AWS cloud services [4] for the infrastructure.</t>
+          <t>A player is an external device that allows content to be played on a non professional screen.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>AU_10</t>
+          <t>P_05</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>AWS RDS</t>
+          <t>Provider</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.8223</v>
+        <v>0.6886</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CF_M09_AU04</t>
+          <t>CF_M09_AU05</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Device</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Player</t>
+          <t>Waapiti Platform</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>A player is an external device that allows content to be played on a non professional screen.</t>
+          <t>The main objective of this work is the development of an asset management module that expands the Waapiti software platform and allows us to solve a series of problems and needs of the company.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>P_05</t>
+          <t>AU_10</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Provider</t>
+          <t>AWS</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.6886</v>
+        <v>0.6004</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CF_M09_AU05</t>
+          <t>CF_M09_AU11</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Waapiti Platform</t>
+          <t>View</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>The main objective of this work is the development of an asset management module that expands the Waapiti software platform and allows us to solve a series of problems and needs of the company.</t>
+          <t>This is the part responsible for displaying information to the user.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>P_05</t>
+          <t>P_04</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Provider</t>
+          <t>Observer</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.598</v>
+        <v>0.7618</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CF_M09_AU07</t>
+          <t>CF_M09_AU12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>client, waapiti platform</t>
-        </is>
-      </c>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Actions</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>On one side is the client, who makes the various requests, and on the other side is the server, who receives and processes them.</t>
+          <t>These are the actions that the user can perform.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>P_01</t>
+          <t>AU_08</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Client-Server</t>
+          <t>React</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.8557</v>
+        <v>0.7452</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CF_M09_AU11</t>
+          <t>CF_M09_AU13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3017,33 +3551,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>View</t>
+          <t>Dispatcher</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>This is the part responsible for displaying information to the user.</t>
+          <t xml:space="preserve"> It is responsible for receiving the actions and sending them to the store to modify its state.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>P_04</t>
+          <t>P_05</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Observer</t>
+          <t>Provider</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.7618</v>
+        <v>0.7081</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CF_M09_AU12</t>
+          <t>CF_M09_AU14</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3053,245 +3587,241 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Actions</t>
+          <t>Store</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>These are the actions that the user can perform.</t>
+          <t>It is responsible for storing the application state.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AU_08</t>
+          <t>P_05</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>React</t>
+          <t>Provider</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.7452</v>
+        <v>0.6902</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CF_M09_AU13</t>
+          <t>CF_M09_AU15</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Component</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Dispatcher</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>actions, store</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> It is responsible for receiving the actions and sending them to the store to modify its state.</t>
+          <t>They are defined as JavaScript objects and indicate the intention to modify the application's state.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>P_05</t>
+          <t>P_06</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Provider</t>
+          <t>Module</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.7081</v>
+        <v>0.6199</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CF_M09_AU14</t>
+          <t>CF_M09_AU16</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Component</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Store</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>dispatcher, store</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>It is responsible for storing the application state.</t>
+          <t>It is responsible for receiving the actions and sending them to the store to modify its state.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>P_05</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Provider</t>
-        </is>
-      </c>
+          <t>AU_20</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>0.6902</v>
+        <v>0.712</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CF_M09_AU15</t>
+          <t>CF_M09_AU18</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>actions, store</t>
-        </is>
-      </c>
+          <t>Layer</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Presentation layer (Backend)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>They are defined as JavaScript objects and indicate the intention to modify the application's state.</t>
+          <t>In this case, the presentation layer is not complex. It corresponds to the user's web browser.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AU_09</t>
+          <t>AU_03</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>NestJS</t>
+          <t>Presentation Layer</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.6073</v>
+        <v>0.9188</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CF_M09_AU16</t>
+          <t>CF_M09_AU23</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>dispatcher, store</t>
-        </is>
-      </c>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>RDS</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>It is responsible for receiving the actions and sending them to the store to modify its state.</t>
+          <t>RDS is a distributed relational database service. In the case of Waapiti, a MySQL database is used and contains all the system information.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AU_17</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
+          <t>AU_22</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
       <c r="H11" t="n">
-        <v>0.6985</v>
+        <v>0.6775</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CF_M09_AU17</t>
+          <t>CF_M09_AU26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Redux</t>
+          <t>User Cache</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Redux is a JavaScript library that allows you to implement the Flux architecture.</t>
+          <t>To improve system response speed, there is a user cache system stored in Amazon DynamoDB</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AU_08</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>React</t>
-        </is>
-      </c>
+          <t>AU_21</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0.7194</v>
+        <v>0.7637</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CF_M09_AU18</t>
+          <t>CF_M09_AU28</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Presentation layer (Backend)</t>
+          <t>Typescript</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>In this case, the presentation layer is not complex. It corresponds to the user's web browser.</t>
+          <t>is a superset of JavaScript. It has been used to develop both the backend.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AU_03</t>
+          <t>AU_17</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Presentation Layer</t>
+          <t>TypeORM</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.9188</v>
+        <v>0.7604</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CF_M09_AU22</t>
+          <t>CF_M09_AU30</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3301,33 +3831,33 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>REST</t>
+          <t>Material UI</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Defines REST API routes and processes requests to send them to the functional service.</t>
+          <t>is a React library that contains user interface components.</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AU_13</t>
+          <t>AU_03</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>HTTP</t>
+          <t>Presentation Layer</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0.6758999999999999</v>
+        <v>0.6683</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CF_M09_AU24</t>
+          <t>CF_M09_AU31</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3337,225 +3867,229 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MySQL</t>
+          <t>NextJS</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS is a distributed relational database service. In the case of Waapiti, a MySQL database is used and contains all the system information.</t>
+          <t>is a React meta-framework that allows you to easily create web applications (since it provides utilities such as web routing).</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>AU_10</t>
+          <t>AU_09</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>AWS RDS</t>
+          <t>NestJS</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0.7068</v>
+        <v>0.7692</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CF_M09_AU26</t>
+          <t>CF_M09_AU32</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>User Cache</t>
+          <t>Shadcn</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>To improve system response speed, there is a user cache system stored in Amazon DynamoDB</t>
+          <t>is a reusable UI component project that features a modern design and focuses on accessibility and ease of customization of components.</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AU_18</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
+          <t>P_05</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Provider</t>
+        </is>
+      </c>
       <c r="H16" t="n">
-        <v>0.7469</v>
+        <v>0.6219</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CF_M09_AU28</t>
+          <t>CF_M09_AU33</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Typescript</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>is a superset of JavaScript. It has been used to develop both the backend.</t>
+          <t>It should be clear that in this project the author has worked on the entire system, both backend and frontend.</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>AU_09</t>
+          <t>AU_04</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>NestJS</t>
+          <t>Business Layer</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0.697</v>
+        <v>0.706</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CF_M09_AU29</t>
+          <t>CF_M09_AU34</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>TypeORM</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>is an ORM (Object Relational Mapping) [41] for TypeScript and JavaScript.</t>
+          <t>It should be clear that in this project the author has worked on the entire system, both backend and frontend.</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>AU_09</t>
+          <t>AU_03</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>NestJS</t>
+          <t>Presentation Layer</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0.6173999999999999</v>
+        <v>0.7635</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CF_M09_AU30</t>
+          <t>CF_M09_AU35</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Material UI</t>
+          <t>Modules</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>is a React library that contains user interface components.</t>
+          <t>Modules are classes that allow NestJS to organize the application.</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>AU_03</t>
+          <t>P_06</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Presentation Layer</t>
+          <t>Module</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>0.6683</v>
+        <v>0.9649</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CF_M09_AU31</t>
+          <t>CF_M09_AU36</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NextJS</t>
+          <t>Controllers</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>is a React meta-framework that allows you to easily create web applications (since it provides utilities such as web routing).</t>
+          <t>Controllers are responsible for receiving and processing HTTP requests.</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>AU_09</t>
+          <t>P_05</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>NestJS</t>
+          <t>Provider</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>0.7692</v>
+        <v>0.6703</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CF_M09_AU32</t>
+          <t>CF_M09_AU37</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Shadcn</t>
+          <t>Providers</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>is a reusable UI component project that features a modern design and focuses on accessibility and ease of customization of components.</t>
+          <t>Providers are classes that can act as services, repositories, factories, helpers, etc.</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -3569,363 +4103,147 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0.6219</v>
+        <v>0.9526</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CF_M09_AU33</t>
+          <t>CF_M09_AU38</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>client, business layer (backend)</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>It should be clear that in this project the author has worked on the entire system, both backend and frontend.</t>
+          <t>Therefore, controllers are responsible for receiving HTTP requests and forwarding them to the providers.</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>AU_04</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Business Layer</t>
-        </is>
-      </c>
+          <t>AU_18</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>0.706</v>
+        <v>0.7089</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CF_M09_AU34</t>
+          <t>CF_M09_AU39</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Data Layer (Backend)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>It should be clear that in this project the author has worked on the entire system, both backend and frontend.</t>
+          <t>The data layer is divided into several AWS services that allow for improved system performance and scalability.</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>AU_03</t>
+          <t>AU_05</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Presentation Layer</t>
+          <t>Data Layer</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>0.7635</v>
+        <v>0.9248</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CF_M09_AU35</t>
+          <t>CF_M09_P06</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Modules</t>
+          <t>Module Pattern</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Modules are classes that allow NestJS to organize the application.</t>
+          <t>This is the most important pattern in the JavaScript language.</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>AU_04</t>
+          <t>P_06</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Business Layer</t>
+          <t>Module</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>0.6216</v>
+        <v>0.9157999999999999</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CF_M09_AU36</t>
+          <t>CF_M09_P08</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Controllers</t>
+          <t>ORM</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Controllers are responsible for receiving and processing HTTP requests.</t>
+          <t>TypeORM is an ORM (Object Relational Mapping) that allows you to define database entities as TypeScript classes.</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>P_05</t>
+          <t>AU_17</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Provider</t>
+          <t>TypeORM</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>0.6703</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>CF_M09_AU37</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Component</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Providers</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Providers are classes that can act as services, repositories, factories, helpers, etc.</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>P_05</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Provider</t>
-        </is>
-      </c>
-      <c r="H26" t="n">
-        <v>0.9526</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>CF_M09_AU38</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>client, business layer (backend)</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Therefore, controllers are responsible for receiving HTTP requests and forwarding them to the providers.</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>AU_16</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="n">
-        <v>0.707</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>CF_M09_AU39</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Layer</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Data Layer (Backend)</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>The data layer is divided into several AWS services that allow for improved system performance and scalability.</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>AU_05</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Data Layer</t>
-        </is>
-      </c>
-      <c r="H28" t="n">
-        <v>0.9248</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>CF_M09_P06</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Design Pattern</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Module Pattern</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>This is the most important pattern in the JavaScript language.</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>AU_04</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Business Layer</t>
-        </is>
-      </c>
-      <c r="H29" t="n">
-        <v>0.6344</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>CF_M09_P07</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Design Pattern</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Hook pattern</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Hooks are a new feature in React that allows you to use state and other React features without writing a class.</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>P_05</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Provider</t>
-        </is>
-      </c>
-      <c r="H30" t="n">
-        <v>0.6149</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>CF_M09_P08</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Design Pattern</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>ORM</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>TypeORM is an ORM (Object Relational Mapping) that allows you to define database entities as TypeScript classes.</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>AU_04</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Business Layer</t>
-        </is>
-      </c>
-      <c r="H31" t="n">
-        <v>0.654</v>
+        <v>0.8084</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/architecture/validation/CF_M09/run_2/CF_M09_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/validation/CF_M09/run_2/CF_M09_arch_eval.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,6 +440,11 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>mean semantic meaning</t>
         </is>
       </c>
@@ -456,7 +461,10 @@
       <c r="C2" t="n">
         <v>0.5</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="n">
+        <v>0.6234</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -475,6 +483,9 @@
         <v>0.5116000000000001</v>
       </c>
       <c r="D3" t="n">
+        <v>0.6471</v>
+      </c>
+      <c r="E3" t="n">
         <v>0.9635</v>
       </c>
     </row>
@@ -491,6 +502,9 @@
         <v>0.4</v>
       </c>
       <c r="D4" t="n">
+        <v>0.4444</v>
+      </c>
+      <c r="E4" t="n">
         <v>0.8169</v>
       </c>
     </row>
@@ -1201,7 +1215,6 @@
       <c r="D2" t="n">
         <v>0.7913</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1222,7 +1235,6 @@
           <t>['AU_06', 'AU_07']</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>AU_19</t>
@@ -1233,7 +1245,6 @@
           <t>business service, functional service</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1252,7 +1263,6 @@
           <t>CF_M09_AU06, CF_M09_AU19</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>CF_M09_AU20</t>
@@ -1308,13 +1318,11 @@
           <t>['AU_04']</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>AU_06</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>Business layer</t>
@@ -1338,13 +1346,11 @@
           <t>CF_M09_P02</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>CF_M09_AU09</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1385,14 +1391,11 @@
           <t>59</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>P_04</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>Observer pattern</t>
@@ -1416,13 +1419,11 @@
           <t>CF_M09_P03</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>CF_M09_P04</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1443,7 +1444,6 @@
       <c r="D5" t="n">
         <v>0.8425</v>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1464,7 +1464,6 @@
           <t>['AU_01', 'AU_02']</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>AU_18</t>
@@ -1475,7 +1474,6 @@
           <t>client, server</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1494,7 +1492,6 @@
           <t>CF_M09_AU06, CF_M09_AU05</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>CF_M09_AU07</t>
@@ -1545,14 +1542,11 @@
           <t>59</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>P_05</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>Provider pattern</t>
@@ -1576,13 +1570,11 @@
           <t>CF_M09_AU01</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>CF_M09_P05</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1623,14 +1615,11 @@
           <t>59</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>P_07</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>Hook pattern</t>
@@ -1654,13 +1643,11 @@
           <t>CF_M09_AU01</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>CF_M09_P07</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1701,14 +1688,11 @@
           <t>55</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>P_01</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>Client-Server Architecture</t>
@@ -1727,14 +1711,11 @@
       <c r="P8" t="n">
         <v>55</v>
       </c>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>CF_M09_P01</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1775,14 +1756,11 @@
           <t>55</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>AU_04</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>Business layer (Backend)</t>
@@ -1806,13 +1784,11 @@
           <t>CF_M09_P02</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>CF_M09_AU19</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1853,14 +1829,11 @@
           <t>55</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>AU_03</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>Presentation layer</t>
@@ -1884,13 +1857,11 @@
           <t>CF_M09_P02</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>CF_M09_AU08</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1931,14 +1902,11 @@
           <t>55</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>AU_05</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>Data layer</t>
@@ -1962,13 +1930,11 @@
           <t>CF_M09_P02</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>CF_M09_AU10</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2014,13 +1980,11 @@
           <t>['AU_03']</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>AU_08</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>React</t>
@@ -2044,13 +2008,11 @@
           <t>CF_M09_AU34</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>CF_M09_AU01</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2096,13 +2058,11 @@
           <t>['AU_05']</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>AU_11</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>MySQL</t>
@@ -2126,13 +2086,11 @@
           <t>CF_M09_AU23</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>CF_M09_AU24</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2178,13 +2136,11 @@
           <t>['AU_18']</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>AU_22</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>REST</t>
@@ -2208,13 +2164,11 @@
           <t>CF_M09_AU20</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>CF_M09_AU22</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2260,13 +2214,11 @@
           <t>['AU_18']</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>AU_14</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>HTTP</t>
@@ -2285,14 +2237,11 @@
       <c r="P15" t="n">
         <v>55</v>
       </c>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
           <t>CF_M09_AU40</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2338,13 +2287,11 @@
           <t>['AU_06', 'AU_07']</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>AU_09</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>NestJS</t>
@@ -2368,13 +2315,11 @@
           <t>CF_M09_AU33</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
           <t>CF_M09_AU02</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2420,13 +2365,11 @@
           <t>['AU_05']</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>AU_17</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>TypeORM</t>
@@ -2450,13 +2393,11 @@
           <t>CF_M09_AU33</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
           <t>CF_M09_AU29</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2497,14 +2438,11 @@
           <t>55</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>AU_01</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>Client</t>
@@ -2528,13 +2466,11 @@
           <t>CF_M09_P01</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
           <t>CF_M09_AU06</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2580,13 +2516,11 @@
           <t>['AU_05']</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>AU_12</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>Amazon S3</t>
@@ -2610,13 +2544,11 @@
           <t>CF_M09_AU39</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
           <t>CF_M09_AU25</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2662,13 +2594,11 @@
           <t>['AU_03']</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>AU_16</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>Redux</t>
@@ -2692,13 +2622,11 @@
           <t>CF_M09_P03</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
           <t>CF_M09_AU17</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2744,13 +2672,11 @@
           <t>['AU_03']</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>P_03</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>Flux</t>
@@ -2774,13 +2700,11 @@
           <t>CF_M09_AU34</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
           <t>CF_M09_P03</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2826,13 +2750,11 @@
           <t>['AU_05']</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>AU_10</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>AWS</t>
@@ -2851,14 +2773,11 @@
       <c r="P22" t="n">
         <v>9</v>
       </c>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
           <t>CF_M09_AU03</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2904,13 +2823,11 @@
           <t>['P_01']</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>P_02</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>Three Layers</t>
@@ -2929,14 +2846,11 @@
       <c r="P23" t="n">
         <v>55</v>
       </c>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
           <t>CF_M09_P02</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2982,13 +2896,11 @@
           <t>['AU_05']</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>AU_13</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t>Amazon DynamoDB</t>
@@ -3012,13 +2924,11 @@
           <t>CF_M09_AU10</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
           <t>CF_M09_AU27</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3064,13 +2974,11 @@
           <t>['AU_19']</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>AU_15</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
           <t>TCP</t>
@@ -3094,13 +3002,11 @@
           <t>CF_M09_AU20</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
           <t>CF_M09_AU21</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3174,7 +3080,6 @@
           <t>Server</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>The server is the software that is responsible for processing user requests.</t>
@@ -3210,7 +3115,6 @@
           <t>Functional Service</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>Service that performs all the important logic of the platform and communicates with the data layer.</t>
@@ -3241,7 +3145,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>functional service, data layer</t>
@@ -3277,7 +3180,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>business service, amazon dynamodb</t>
@@ -3318,7 +3220,6 @@
           <t>Module</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>This pattern allows encapsulating information and exposing only what is desired to be shared between modules.</t>
@@ -3410,7 +3311,6 @@
           <t>Player</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>A player is an external device that allows content to be played on a non professional screen.</t>
@@ -3446,7 +3346,6 @@
           <t>Waapiti Platform</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>The main objective of this work is the development of an asset management module that expands the Waapiti software platform and allows us to solve a series of problems and needs of the company.</t>
@@ -3482,7 +3381,6 @@
           <t>View</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>This is the part responsible for displaying information to the user.</t>
@@ -3518,7 +3416,6 @@
           <t>Actions</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>These are the actions that the user can perform.</t>
@@ -3554,7 +3451,6 @@
           <t>Dispatcher</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t xml:space="preserve"> It is responsible for receiving the actions and sending them to the store to modify its state.</t>
@@ -3590,7 +3486,6 @@
           <t>Store</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>It is responsible for storing the application state.</t>
@@ -3621,7 +3516,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>actions, store</t>
@@ -3657,7 +3551,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>dispatcher, store</t>
@@ -3673,7 +3566,6 @@
           <t>AU_20</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>0.712</v>
       </c>
@@ -3694,7 +3586,6 @@
           <t>Presentation layer (Backend)</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>In this case, the presentation layer is not complex. It corresponds to the user's web browser.</t>
@@ -3730,7 +3621,6 @@
           <t>RDS</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>RDS is a distributed relational database service. In the case of Waapiti, a MySQL database is used and contains all the system information.</t>
@@ -3766,7 +3656,6 @@
           <t>User Cache</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>To improve system response speed, there is a user cache system stored in Amazon DynamoDB</t>
@@ -3777,7 +3666,6 @@
           <t>AU_21</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>0.7637</v>
       </c>
@@ -3798,7 +3686,6 @@
           <t>Typescript</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>is a superset of JavaScript. It has been used to develop both the backend.</t>
@@ -3834,7 +3721,6 @@
           <t>Material UI</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>is a React library that contains user interface components.</t>
@@ -3870,7 +3756,6 @@
           <t>NextJS</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>is a React meta-framework that allows you to easily create web applications (since it provides utilities such as web routing).</t>
@@ -3906,7 +3791,6 @@
           <t>Shadcn</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>is a reusable UI component project that features a modern design and focuses on accessibility and ease of customization of components.</t>
@@ -3942,7 +3826,6 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>It should be clear that in this project the author has worked on the entire system, both backend and frontend.</t>
@@ -3978,7 +3861,6 @@
           <t>Frontend</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>It should be clear that in this project the author has worked on the entire system, both backend and frontend.</t>
@@ -4014,7 +3896,6 @@
           <t>Modules</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>Modules are classes that allow NestJS to organize the application.</t>
@@ -4050,7 +3931,6 @@
           <t>Controllers</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>Controllers are responsible for receiving and processing HTTP requests.</t>
@@ -4086,7 +3966,6 @@
           <t>Providers</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>Providers are classes that can act as services, repositories, factories, helpers, etc.</t>
@@ -4117,7 +3996,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
           <t>client, business layer (backend)</t>
@@ -4133,7 +4011,6 @@
           <t>AU_18</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>0.7089</v>
       </c>
@@ -4154,7 +4031,6 @@
           <t>Data Layer (Backend)</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>The data layer is divided into several AWS services that allow for improved system performance and scalability.</t>
@@ -4190,7 +4066,6 @@
           <t>Module Pattern</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t>This is the most important pattern in the JavaScript language.</t>
@@ -4226,7 +4101,6 @@
           <t>ORM</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>TypeORM is an ORM (Object Relational Mapping) that allows you to define database entities as TypeScript classes.</t>
